--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503189362\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{142F03DB-E62B-4870-8AAD-24C36611113D}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6031FC3-036A-4E9D-9C37-B4A319DDB356}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
-    <sheet name="合同" sheetId="1" r:id="rId1"/>
-    <sheet name="课程" sheetId="2" r:id="rId2"/>
+    <sheet name="Contract" sheetId="1" r:id="rId1"/>
+    <sheet name="Contract_Course" sheetId="2" r:id="rId2"/>
+    <sheet name="Contract_Asset" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
   <si>
     <t>代理商</t>
   </si>
@@ -74,13 +75,40 @@
   </si>
   <si>
     <t>区域</t>
+  </si>
+  <si>
+    <t>设备二维码</t>
+  </si>
+  <si>
+    <t>高低端机</t>
+  </si>
+  <si>
+    <t>Sub Region</t>
+  </si>
+  <si>
+    <t>Modality</t>
+  </si>
+  <si>
+    <t>责任工程师</t>
+  </si>
+  <si>
+    <t>KA</t>
+  </si>
+  <si>
+    <t>是否删除</t>
+  </si>
+  <si>
+    <t>合同状态</t>
+  </si>
+  <si>
+    <t>Region</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -96,17 +124,43 @@
     </font>
     <font>
       <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4F5F7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -136,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -144,11 +198,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -463,13 +520,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="10" max="10" width="10.77734375" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" customWidth="1"/>
+    <col min="11" max="11" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>13</v>
       </c>
@@ -488,34 +548,24 @@
       <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -525,30 +575,74 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD4DBF4-FEF1-4385-BAD9-BD07A4FA541B}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEEB4E3A-F934-494E-85E2-577CC5C4A5F0}">
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultColWidth="7.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="12.33203125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" customWidth="1"/>
+    <col min="8" max="8" width="19.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="6" customFormat="1" ht="10.199999999999999" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6031FC3-036A-4E9D-9C37-B4A319DDB356}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7F1447-812A-4E00-86C6-64BE5F91D147}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
-    <sheet name="Contract" sheetId="1" r:id="rId1"/>
-    <sheet name="Contract_Course" sheetId="2" r:id="rId2"/>
-    <sheet name="Contract_Asset" sheetId="3" r:id="rId3"/>
+    <sheet name="合同" sheetId="1" r:id="rId1"/>
+    <sheet name="相关课程" sheetId="2" r:id="rId2"/>
+    <sheet name="相关设备" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7F1447-812A-4E00-86C6-64BE5F91D147}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EAA75E1-4276-48E9-A666-E1AF407E2C0A}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>代理商</t>
   </si>
@@ -96,31 +96,19 @@
   </si>
   <si>
     <t>是否删除</t>
-  </si>
-  <si>
-    <t>合同状态</t>
-  </si>
-  <si>
-    <t>Region</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <color rgb="FF172B4D"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -131,36 +119,22 @@
     </font>
     <font>
       <sz val="8"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="12"/>
+      <color rgb="FF172B4D"/>
+      <name val="宋体"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4F5F7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -190,22 +164,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -520,50 +486,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" customWidth="1"/>
+    <col min="9" max="9" width="16.77734375" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:11" s="4" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
@@ -577,29 +544,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD4DBF4-FEF1-4385-BAD9-BD07A4FA541B}">
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="12.77734375" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" customWidth="1"/>
+    <col min="5" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="8" t="s">
+    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -609,39 +581,44 @@
   <dimension ref="A1:H1"/>
   <sheetFormatPr defaultColWidth="7.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.33203125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="9.44140625" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="7" max="7" width="15.109375" customWidth="1"/>
     <col min="8" max="8" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="6" customFormat="1" ht="10.199999999999999" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="3" t="s">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EAA75E1-4276-48E9-A666-E1AF407E2C0A}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF06317-90D5-4AA4-A140-B1C1F31D5CED}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-28920" yWindow="1155" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>代理商</t>
   </si>
@@ -542,31 +542,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD4DBF4-FEF1-4385-BAD9-BD07A4FA541B}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.77734375" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" customWidth="1"/>
-    <col min="5" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.88671875" customWidth="1"/>
+    <col min="3" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="3" t="s">
         <v>12</v>
       </c>
     </row>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF06317-90D5-4AA4-A140-B1C1F31D5CED}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E36C4B4-923D-4FFE-B0FF-C39C8337A35E}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1155" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
   <si>
     <t>代理商</t>
   </si>
@@ -50,30 +50,15 @@
     <t>IB数量</t>
   </si>
   <si>
-    <t>备件名额</t>
-  </si>
-  <si>
-    <t>探头名额</t>
-  </si>
-  <si>
-    <t>人工支持次数</t>
-  </si>
-  <si>
     <t>课程名称</t>
   </si>
   <si>
-    <t>备件+人工+保养</t>
-  </si>
-  <si>
     <t>合同号</t>
   </si>
   <si>
     <t>课程ID</t>
   </si>
   <si>
-    <t>课程额度</t>
-  </si>
-  <si>
     <t>区域</t>
   </si>
   <si>
@@ -96,6 +81,51 @@
   </si>
   <si>
     <t>是否删除</t>
+  </si>
+  <si>
+    <t>课程总额</t>
+  </si>
+  <si>
+    <t>课程剩余名额</t>
+  </si>
+  <si>
+    <t>课程申请名额</t>
+  </si>
+  <si>
+    <t>备件总额</t>
+  </si>
+  <si>
+    <t>备件剩余名额</t>
+  </si>
+  <si>
+    <t>备件申请名额</t>
+  </si>
+  <si>
+    <t>探头总额</t>
+  </si>
+  <si>
+    <t>探头剩余名额</t>
+  </si>
+  <si>
+    <t>探头申请名额</t>
+  </si>
+  <si>
+    <t>人工支持总次数</t>
+  </si>
+  <si>
+    <t>人工支持剩余次数</t>
+  </si>
+  <si>
+    <t>人工支持申请次数</t>
+  </si>
+  <si>
+    <t>备件+人工+保养总额</t>
+  </si>
+  <si>
+    <t>备件+人工+保养剩余名额</t>
+  </si>
+  <si>
+    <t>备件+人工+保养申请名额</t>
   </si>
 </sst>
 </file>
@@ -164,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -172,6 +202,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -486,28 +519,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.109375" customWidth="1"/>
-    <col min="8" max="8" width="15.88671875" customWidth="1"/>
-    <col min="9" max="9" width="16.77734375" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5546875" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.21875" customWidth="1"/>
+    <col min="12" max="12" width="16.88671875" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" customWidth="1"/>
+    <col min="14" max="14" width="16.77734375" customWidth="1"/>
+    <col min="15" max="15" width="19.44140625" customWidth="1"/>
+    <col min="16" max="16" width="19.33203125" customWidth="1"/>
+    <col min="17" max="17" width="23.21875" customWidth="1"/>
+    <col min="18" max="18" width="26.5546875" customWidth="1"/>
+    <col min="19" max="19" width="24.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="4" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" s="4" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>1</v>
@@ -521,17 +561,41 @@
       <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>6</v>
+      <c r="H1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -542,30 +606,40 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD4DBF4-FEF1-4385-BAD9-BD07A4FA541B}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.88671875" customWidth="1"/>
-    <col min="3" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>12</v>
+        <v>5</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -586,28 +660,28 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E36C4B4-923D-4FFE-B0FF-C39C8337A35E}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF06317-90D5-4AA4-A140-B1C1F31D5CED}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1155" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>代理商</t>
   </si>
@@ -50,15 +50,30 @@
     <t>IB数量</t>
   </si>
   <si>
+    <t>备件名额</t>
+  </si>
+  <si>
+    <t>探头名额</t>
+  </si>
+  <si>
+    <t>人工支持次数</t>
+  </si>
+  <si>
     <t>课程名称</t>
   </si>
   <si>
+    <t>备件+人工+保养</t>
+  </si>
+  <si>
     <t>合同号</t>
   </si>
   <si>
     <t>课程ID</t>
   </si>
   <si>
+    <t>课程额度</t>
+  </si>
+  <si>
     <t>区域</t>
   </si>
   <si>
@@ -81,51 +96,6 @@
   </si>
   <si>
     <t>是否删除</t>
-  </si>
-  <si>
-    <t>课程总额</t>
-  </si>
-  <si>
-    <t>课程剩余名额</t>
-  </si>
-  <si>
-    <t>课程申请名额</t>
-  </si>
-  <si>
-    <t>备件总额</t>
-  </si>
-  <si>
-    <t>备件剩余名额</t>
-  </si>
-  <si>
-    <t>备件申请名额</t>
-  </si>
-  <si>
-    <t>探头总额</t>
-  </si>
-  <si>
-    <t>探头剩余名额</t>
-  </si>
-  <si>
-    <t>探头申请名额</t>
-  </si>
-  <si>
-    <t>人工支持总次数</t>
-  </si>
-  <si>
-    <t>人工支持剩余次数</t>
-  </si>
-  <si>
-    <t>人工支持申请次数</t>
-  </si>
-  <si>
-    <t>备件+人工+保养总额</t>
-  </si>
-  <si>
-    <t>备件+人工+保养剩余名额</t>
-  </si>
-  <si>
-    <t>备件+人工+保养申请名额</t>
   </si>
 </sst>
 </file>
@@ -194,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -202,9 +172,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -519,35 +486,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.109375" customWidth="1"/>
-    <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.21875" customWidth="1"/>
-    <col min="12" max="12" width="16.88671875" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" customWidth="1"/>
-    <col min="14" max="14" width="16.77734375" customWidth="1"/>
-    <col min="15" max="15" width="19.44140625" customWidth="1"/>
-    <col min="16" max="16" width="19.33203125" customWidth="1"/>
-    <col min="17" max="17" width="23.21875" customWidth="1"/>
-    <col min="18" max="18" width="26.5546875" customWidth="1"/>
-    <col min="19" max="19" width="24.88671875" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" customWidth="1"/>
+    <col min="9" max="9" width="16.77734375" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="4" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="4" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>1</v>
@@ -561,41 +521,17 @@
       <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="R1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="S1" s="5" t="s">
-        <v>30</v>
+      <c r="H1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -606,40 +542,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD4DBF4-FEF1-4385-BAD9-BD07A4FA541B}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.88671875" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" customWidth="1"/>
+    <col min="3" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>18</v>
+        <v>8</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -660,28 +586,28 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E36C4B4-923D-4FFE-B0FF-C39C8337A35E}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1FD2819-747F-4DEC-BA7C-DD5D8FA5393F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1155" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
   <si>
     <t>代理商</t>
   </si>
@@ -126,6 +126,21 @@
   </si>
   <si>
     <t>备件+人工+保养申请名额</t>
+  </si>
+  <si>
+    <t>课程已使用名额</t>
+  </si>
+  <si>
+    <t>备件已使用名额</t>
+  </si>
+  <si>
+    <t>探头已使用名额</t>
+  </si>
+  <si>
+    <t>人工支持已使用次数</t>
+  </si>
+  <si>
+    <t>备件+人工+保养已使用名额</t>
   </si>
 </sst>
 </file>
@@ -519,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:W1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
@@ -528,18 +543,22 @@
     <col min="6" max="6" width="15.109375" customWidth="1"/>
     <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.21875" customWidth="1"/>
-    <col min="12" max="12" width="16.88671875" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" customWidth="1"/>
-    <col min="14" max="14" width="16.77734375" customWidth="1"/>
-    <col min="15" max="15" width="19.44140625" customWidth="1"/>
-    <col min="16" max="16" width="19.33203125" customWidth="1"/>
-    <col min="17" max="17" width="23.21875" customWidth="1"/>
-    <col min="18" max="18" width="26.5546875" customWidth="1"/>
-    <col min="19" max="19" width="24.88671875" customWidth="1"/>
+    <col min="11" max="11" width="18.44140625" customWidth="1"/>
+    <col min="12" max="12" width="13.21875" customWidth="1"/>
+    <col min="13" max="13" width="16.88671875" customWidth="1"/>
+    <col min="14" max="14" width="14.6640625" customWidth="1"/>
+    <col min="15" max="15" width="17.21875" customWidth="1"/>
+    <col min="16" max="16" width="16.77734375" customWidth="1"/>
+    <col min="17" max="17" width="19.44140625" customWidth="1"/>
+    <col min="18" max="18" width="19.33203125" customWidth="1"/>
+    <col min="19" max="19" width="21.44140625" customWidth="1"/>
+    <col min="20" max="20" width="23.21875" customWidth="1"/>
+    <col min="21" max="21" width="26.5546875" customWidth="1"/>
+    <col min="22" max="22" width="24.88671875" customWidth="1"/>
+    <col min="23" max="23" width="29.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="4" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" s="4" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
@@ -571,31 +590,43 @@
         <v>21</v>
       </c>
       <c r="K1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="P1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="S1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="T1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="U1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>30</v>
+      </c>
+      <c r="W1" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -606,7 +637,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD4DBF4-FEF1-4385-BAD9-BD07A4FA541B}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.88671875" customWidth="1"/>
@@ -614,9 +645,10 @@
     <col min="4" max="4" width="15.88671875" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="17.33203125" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -634,6 +666,9 @@
       </c>
       <c r="F1" s="5" t="s">
         <v>18</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1FD2819-747F-4DEC-BA7C-DD5D8FA5393F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{498F5AE7-90BA-423F-8869-6F3141D7DD7D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-28920" yWindow="1155" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
   <si>
     <t>代理商</t>
   </si>
@@ -89,43 +89,28 @@
     <t>课程剩余名额</t>
   </si>
   <si>
-    <t>课程申请名额</t>
-  </si>
-  <si>
     <t>备件总额</t>
   </si>
   <si>
     <t>备件剩余名额</t>
   </si>
   <si>
-    <t>备件申请名额</t>
-  </si>
-  <si>
     <t>探头总额</t>
   </si>
   <si>
     <t>探头剩余名额</t>
   </si>
   <si>
-    <t>探头申请名额</t>
-  </si>
-  <si>
     <t>人工支持总次数</t>
   </si>
   <si>
     <t>人工支持剩余次数</t>
   </si>
   <si>
-    <t>人工支持申请次数</t>
-  </si>
-  <si>
     <t>备件+人工+保养总额</t>
   </si>
   <si>
     <t>备件+人工+保养剩余名额</t>
-  </si>
-  <si>
-    <t>备件+人工+保养申请名额</t>
   </si>
   <si>
     <t>课程已使用名额</t>
@@ -534,7 +519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
@@ -542,23 +527,20 @@
     <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.109375" customWidth="1"/>
     <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.44140625" customWidth="1"/>
-    <col min="12" max="12" width="13.21875" customWidth="1"/>
-    <col min="13" max="13" width="16.88671875" customWidth="1"/>
-    <col min="14" max="14" width="14.6640625" customWidth="1"/>
-    <col min="15" max="15" width="17.21875" customWidth="1"/>
-    <col min="16" max="16" width="16.77734375" customWidth="1"/>
-    <col min="17" max="17" width="19.44140625" customWidth="1"/>
-    <col min="18" max="18" width="19.33203125" customWidth="1"/>
-    <col min="19" max="19" width="21.44140625" customWidth="1"/>
-    <col min="20" max="20" width="23.21875" customWidth="1"/>
-    <col min="21" max="21" width="26.5546875" customWidth="1"/>
-    <col min="22" max="22" width="24.88671875" customWidth="1"/>
-    <col min="23" max="23" width="29.109375" customWidth="1"/>
+    <col min="9" max="9" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.44140625" customWidth="1"/>
+    <col min="11" max="11" width="13.21875" customWidth="1"/>
+    <col min="12" max="12" width="16.88671875" customWidth="1"/>
+    <col min="13" max="13" width="17.21875" customWidth="1"/>
+    <col min="14" max="14" width="16.77734375" customWidth="1"/>
+    <col min="15" max="15" width="19.44140625" customWidth="1"/>
+    <col min="16" max="16" width="21.44140625" customWidth="1"/>
+    <col min="17" max="17" width="23.21875" customWidth="1"/>
+    <col min="18" max="18" width="26.5546875" customWidth="1"/>
+    <col min="19" max="19" width="29.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="4" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" s="4" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
@@ -581,52 +563,40 @@
         <v>4</v>
       </c>
       <c r="H1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="P1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="O1" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="P1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="Q1" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="R1" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="S1" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="T1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="V1" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="W1" s="5" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -637,18 +607,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD4DBF4-FEF1-4385-BAD9-BD07A4FA541B}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.88671875" customWidth="1"/>
     <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.88671875" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -665,10 +634,7 @@
         <v>17</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{498F5AE7-90BA-423F-8869-6F3141D7DD7D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B301C6FB-84CD-413C-B0D2-08538BA62CD8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1155" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
   <si>
     <t>代理商</t>
   </si>
@@ -126,6 +126,9 @@
   </si>
   <si>
     <t>备件+人工+保养已使用名额</t>
+  </si>
+  <si>
+    <t>备注</t>
   </si>
 </sst>
 </file>
@@ -194,7 +197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -204,6 +207,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -519,28 +532,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:S1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:T12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.109375" customWidth="1"/>
-    <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.44140625" customWidth="1"/>
-    <col min="11" max="11" width="13.21875" customWidth="1"/>
-    <col min="12" max="12" width="16.88671875" customWidth="1"/>
-    <col min="13" max="13" width="17.21875" customWidth="1"/>
-    <col min="14" max="14" width="16.77734375" customWidth="1"/>
-    <col min="15" max="15" width="19.44140625" customWidth="1"/>
-    <col min="16" max="16" width="21.44140625" customWidth="1"/>
-    <col min="17" max="17" width="23.21875" customWidth="1"/>
-    <col min="18" max="18" width="26.5546875" customWidth="1"/>
-    <col min="19" max="19" width="29.109375" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="8" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.42578125" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" customWidth="1"/>
+    <col min="12" max="12" width="16.85546875" customWidth="1"/>
+    <col min="13" max="13" width="17.28515625" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" customWidth="1"/>
+    <col min="15" max="15" width="19.42578125" customWidth="1"/>
+    <col min="16" max="16" width="21.42578125" customWidth="1"/>
+    <col min="17" max="17" width="23.28515625" customWidth="1"/>
+    <col min="18" max="18" width="26.5703125" customWidth="1"/>
+    <col min="19" max="19" width="29.140625" customWidth="1"/>
+    <col min="20" max="20" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="4" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
@@ -553,10 +567,10 @@
       <c r="D1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
@@ -598,6 +612,12 @@
       <c r="S1" s="5" t="s">
         <v>30</v>
       </c>
+      <c r="T1" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="E12" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -608,16 +628,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD4DBF4-FEF1-4385-BAD9-BD07A4FA541B}">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.88671875" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -647,19 +667,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEEB4E3A-F934-494E-85E2-577CC5C4A5F0}">
   <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultColWidth="7.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="7.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.21875" customWidth="1"/>
-    <col min="4" max="4" width="14.5546875" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
-    <col min="7" max="7" width="15.109375" customWidth="1"/>
-    <col min="8" max="8" width="19.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="8" max="8" width="19.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B301C6FB-84CD-413C-B0D2-08538BA62CD8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{019659B5-73C4-441B-A5F9-2BDAB73AA292}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
     <sheet name="相关课程" sheetId="2" r:id="rId2"/>
     <sheet name="相关设备" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -80,55 +80,55 @@
     <t>KA</t>
   </si>
   <si>
+    <t>课程总额</t>
+  </si>
+  <si>
+    <t>课程剩余名额</t>
+  </si>
+  <si>
+    <t>备件总额</t>
+  </si>
+  <si>
+    <t>备件剩余名额</t>
+  </si>
+  <si>
+    <t>探头总额</t>
+  </si>
+  <si>
+    <t>探头剩余名额</t>
+  </si>
+  <si>
+    <t>人工支持总次数</t>
+  </si>
+  <si>
+    <t>人工支持剩余次数</t>
+  </si>
+  <si>
+    <t>备件+人工+保养总额</t>
+  </si>
+  <si>
+    <t>备件+人工+保养剩余名额</t>
+  </si>
+  <si>
+    <t>课程已使用名额</t>
+  </si>
+  <si>
+    <t>备件已使用名额</t>
+  </si>
+  <si>
+    <t>探头已使用名额</t>
+  </si>
+  <si>
+    <t>人工支持已使用次数</t>
+  </si>
+  <si>
+    <t>备件+人工+保养已使用名额</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
     <t>是否删除</t>
-  </si>
-  <si>
-    <t>课程总额</t>
-  </si>
-  <si>
-    <t>课程剩余名额</t>
-  </si>
-  <si>
-    <t>备件总额</t>
-  </si>
-  <si>
-    <t>备件剩余名额</t>
-  </si>
-  <si>
-    <t>探头总额</t>
-  </si>
-  <si>
-    <t>探头剩余名额</t>
-  </si>
-  <si>
-    <t>人工支持总次数</t>
-  </si>
-  <si>
-    <t>人工支持剩余次数</t>
-  </si>
-  <si>
-    <t>备件+人工+保养总额</t>
-  </si>
-  <si>
-    <t>备件+人工+保养剩余名额</t>
-  </si>
-  <si>
-    <t>课程已使用名额</t>
-  </si>
-  <si>
-    <t>备件已使用名额</t>
-  </si>
-  <si>
-    <t>探头已使用名额</t>
-  </si>
-  <si>
-    <t>人工支持已使用次数</t>
-  </si>
-  <si>
-    <t>备件+人工+保养已使用名额</t>
-  </si>
-  <si>
-    <t>备注</t>
   </si>
 </sst>
 </file>
@@ -577,43 +577,43 @@
         <v>4</v>
       </c>
       <c r="H1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="L1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="O1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="P1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="N1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="O1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="R1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="S1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="Q1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="R1" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="S1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="T1" s="5" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -648,13 +648,13 @@
         <v>5</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>17</v>
-      </c>
       <c r="F1" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -676,7 +676,7 @@
     <col min="5" max="5" width="12.42578125" customWidth="1"/>
     <col min="6" max="6" width="14.7109375" customWidth="1"/>
     <col min="7" max="7" width="15.140625" customWidth="1"/>
-    <col min="8" max="8" width="19.28515625" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -702,11 +702,16 @@
         <v>14</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576" xr:uid="{B075DA68-B71A-4E5B-9F5B-32052F1603BD}">
+      <formula1>"超声高端机,超声低端机,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{019659B5-73C4-441B-A5F9-2BDAB73AA292}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FE9CA0D-68E9-40B4-8108-7129FB9CB02E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
     <sheet name="相关课程" sheetId="2" r:id="rId2"/>
     <sheet name="相关设备" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
   <si>
     <t>代理商</t>
   </si>
@@ -129,6 +129,9 @@
   </si>
   <si>
     <t>是否删除</t>
+  </si>
+  <si>
+    <t>维修类型</t>
   </si>
 </sst>
 </file>
@@ -666,7 +669,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEEB4E3A-F934-494E-85E2-577CC5C4A5F0}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultColWidth="7.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -675,11 +678,11 @@
     <col min="4" max="4" width="14.5703125" customWidth="1"/>
     <col min="5" max="5" width="12.42578125" customWidth="1"/>
     <col min="6" max="6" width="14.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" customWidth="1"/>
-    <col min="8" max="8" width="15.42578125" customWidth="1"/>
+    <col min="7" max="8" width="15.140625" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -702,14 +705,20 @@
         <v>14</v>
       </c>
       <c r="H1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>31</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576" xr:uid="{B075DA68-B71A-4E5B-9F5B-32052F1603BD}">
       <formula1>"超声高端机,超声低端机,N/A"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576" xr:uid="{B1DF22E0-479B-4685-B17A-2952F9A994AD}">
+      <formula1>"内修,外修,内外修可选"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FE9CA0D-68E9-40B4-8108-7129FB9CB02E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F14E66C-6AE4-4EDD-87F7-82114D199C01}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
   <si>
     <t>代理商</t>
   </si>
@@ -95,9 +95,6 @@
     <t>探头总额</t>
   </si>
   <si>
-    <t>探头剩余名额</t>
-  </si>
-  <si>
     <t>人工支持总次数</t>
   </si>
   <si>
@@ -132,6 +129,18 @@
   </si>
   <si>
     <t>维修类型</t>
+  </si>
+  <si>
+    <t>探头任意剩余名额</t>
+  </si>
+  <si>
+    <t>探头普通剩余名额</t>
+  </si>
+  <si>
+    <t>探头特殊剩余名额</t>
+  </si>
+  <si>
+    <t>探头高值剩余名额</t>
   </si>
 </sst>
 </file>
@@ -535,7 +544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:W12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -546,18 +555,18 @@
     <col min="9" max="9" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.42578125" customWidth="1"/>
     <col min="11" max="11" width="13.28515625" customWidth="1"/>
-    <col min="12" max="12" width="16.85546875" customWidth="1"/>
-    <col min="13" max="13" width="17.28515625" customWidth="1"/>
-    <col min="14" max="14" width="16.7109375" customWidth="1"/>
-    <col min="15" max="15" width="19.42578125" customWidth="1"/>
-    <col min="16" max="16" width="21.42578125" customWidth="1"/>
-    <col min="17" max="17" width="23.28515625" customWidth="1"/>
-    <col min="18" max="18" width="26.5703125" customWidth="1"/>
-    <col min="19" max="19" width="29.140625" customWidth="1"/>
-    <col min="20" max="20" width="16.42578125" customWidth="1"/>
+    <col min="12" max="15" width="21.85546875" customWidth="1"/>
+    <col min="16" max="16" width="17.28515625" customWidth="1"/>
+    <col min="17" max="17" width="16.7109375" customWidth="1"/>
+    <col min="18" max="18" width="19.42578125" customWidth="1"/>
+    <col min="19" max="19" width="21.42578125" customWidth="1"/>
+    <col min="20" max="20" width="23.28515625" customWidth="1"/>
+    <col min="21" max="21" width="26.5703125" customWidth="1"/>
+    <col min="22" max="22" width="29.140625" customWidth="1"/>
+    <col min="23" max="23" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
@@ -586,40 +595,49 @@
         <v>18</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>19</v>
       </c>
       <c r="L1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="R1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="N1" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="U1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="V1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="Q1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="R1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="T1" s="5" t="s">
-        <v>30</v>
-      </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="E12" s="7"/>
     </row>
   </sheetData>
@@ -657,7 +675,7 @@
         <v>16</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -705,10 +723,10 @@
         <v>14</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (11)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F14E66C-6AE4-4EDD-87F7-82114D199C01}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5511D1B0-D5EA-41DA-BC54-0D4BC003F5D5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
   <si>
     <t>代理商</t>
   </si>
@@ -141,13 +141,19 @@
   </si>
   <si>
     <t>探头高值剩余名额</t>
+  </si>
+  <si>
+    <t>培训合同号</t>
+  </si>
+  <si>
+    <t>modality</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -232,7 +238,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -248,7 +254,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -545,28 +551,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
   <dimension ref="A1:W12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="8" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.42578125" customWidth="1"/>
-    <col min="11" max="11" width="13.28515625" customWidth="1"/>
-    <col min="12" max="15" width="21.85546875" customWidth="1"/>
-    <col min="16" max="16" width="17.28515625" customWidth="1"/>
-    <col min="17" max="17" width="16.7109375" customWidth="1"/>
-    <col min="18" max="18" width="19.42578125" customWidth="1"/>
-    <col min="19" max="19" width="21.42578125" customWidth="1"/>
-    <col min="20" max="20" width="23.28515625" customWidth="1"/>
-    <col min="21" max="21" width="26.5703125" customWidth="1"/>
-    <col min="22" max="22" width="29.140625" customWidth="1"/>
-    <col min="23" max="23" width="16.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" style="8" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.44140625" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" customWidth="1"/>
+    <col min="12" max="15" width="21.88671875" customWidth="1"/>
+    <col min="16" max="16" width="17.33203125" customWidth="1"/>
+    <col min="17" max="17" width="16.6640625" customWidth="1"/>
+    <col min="18" max="18" width="19.44140625" customWidth="1"/>
+    <col min="19" max="19" width="21.44140625" customWidth="1"/>
+    <col min="20" max="20" width="23.33203125" customWidth="1"/>
+    <col min="21" max="21" width="26.5546875" customWidth="1"/>
+    <col min="22" max="22" width="29.109375" customWidth="1"/>
+    <col min="23" max="23" width="16.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" s="4" customFormat="1" ht="28.5" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
@@ -637,7 +643,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23">
       <c r="E12" s="7"/>
     </row>
   </sheetData>
@@ -648,33 +654,42 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD4DBF4-FEF1-4385-BAD9-BD07A4FA541B}">
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.88671875" customWidth="1"/>
+    <col min="2" max="2" width="19.5546875" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="4" max="4" width="17.77734375" customWidth="1"/>
+    <col min="5" max="5" width="20.88671875" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15.6">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>24</v>
       </c>
     </row>
@@ -688,19 +703,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEEB4E3A-F934-494E-85E2-577CC5C4A5F0}">
   <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultColWidth="7.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="7.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
-    <col min="7" max="8" width="15.140625" customWidth="1"/>
-    <col min="9" max="9" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="7" max="8" width="15.109375" customWidth="1"/>
+    <col min="9" max="9" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="15.6">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (11)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5511D1B0-D5EA-41DA-BC54-0D4BC003F5D5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06C4A4B-14A2-464D-BED4-E8DF83ADDABB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
   <si>
     <t>代理商</t>
   </si>
@@ -92,9 +92,6 @@
     <t>备件剩余名额</t>
   </si>
   <si>
-    <t>探头总额</t>
-  </si>
-  <si>
     <t>人工支持总次数</t>
   </si>
   <si>
@@ -113,9 +110,6 @@
     <t>备件已使用名额</t>
   </si>
   <si>
-    <t>探头已使用名额</t>
-  </si>
-  <si>
     <t>人工支持已使用次数</t>
   </si>
   <si>
@@ -147,13 +141,37 @@
   </si>
   <si>
     <t>modality</t>
+  </si>
+  <si>
+    <t>探头特殊已使用名额</t>
+  </si>
+  <si>
+    <t>探头高值总额</t>
+  </si>
+  <si>
+    <t>探头高值已使用名额</t>
+  </si>
+  <si>
+    <t>探头任意总额</t>
+  </si>
+  <si>
+    <t>探头任意已使用名额</t>
+  </si>
+  <si>
+    <t>探头普通总额</t>
+  </si>
+  <si>
+    <t>探头普通已使用名额</t>
+  </si>
+  <si>
+    <t>探头特殊总额</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -215,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -226,19 +244,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -254,7 +266,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -550,48 +562,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:W12"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:AC12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="14.44140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.109375" style="8" customWidth="1"/>
-    <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.44140625" customWidth="1"/>
-    <col min="11" max="11" width="13.33203125" customWidth="1"/>
-    <col min="12" max="15" width="21.88671875" customWidth="1"/>
-    <col min="16" max="16" width="17.33203125" customWidth="1"/>
-    <col min="17" max="17" width="16.6640625" customWidth="1"/>
-    <col min="18" max="18" width="19.44140625" customWidth="1"/>
-    <col min="19" max="19" width="21.44140625" customWidth="1"/>
-    <col min="20" max="20" width="23.33203125" customWidth="1"/>
-    <col min="21" max="21" width="26.5546875" customWidth="1"/>
-    <col min="22" max="22" width="29.109375" customWidth="1"/>
-    <col min="23" max="23" width="16.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="7" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.42578125" customWidth="1"/>
+    <col min="11" max="11" width="15.85546875" customWidth="1"/>
+    <col min="12" max="21" width="21.85546875" customWidth="1"/>
+    <col min="22" max="22" width="17.28515625" customWidth="1"/>
+    <col min="23" max="23" width="16.7109375" customWidth="1"/>
+    <col min="24" max="24" width="19.42578125" customWidth="1"/>
+    <col min="25" max="25" width="21.42578125" customWidth="1"/>
+    <col min="26" max="26" width="23.28515625" customWidth="1"/>
+    <col min="27" max="27" width="26.5703125" customWidth="1"/>
+    <col min="28" max="28" width="29.140625" customWidth="1"/>
+    <col min="29" max="29" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="4" customFormat="1" ht="28.5" customHeight="1">
+    <row r="1" spans="1:29" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="5" t="s">
@@ -601,50 +613,68 @@
         <v>18</v>
       </c>
       <c r="J1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="W1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="X1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="P1" s="5" t="s">
+      <c r="Z1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="Q1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="R1" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="S1" s="5" t="s">
+      <c r="AC1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="T1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="V1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="W1" s="5" t="s">
-        <v>29</v>
-      </c>
     </row>
-    <row r="12" spans="1:23">
-      <c r="E12" s="7"/>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="E12" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -655,24 +685,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD4DBF4-FEF1-4385-BAD9-BD07A4FA541B}">
   <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.88671875" customWidth="1"/>
-    <col min="2" max="2" width="19.5546875" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="17.77734375" customWidth="1"/>
-    <col min="5" max="5" width="20.88671875" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.6">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>7</v>
@@ -681,7 +711,7 @@
         <v>5</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>15</v>
@@ -690,7 +720,7 @@
         <v>16</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -703,19 +733,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEEB4E3A-F934-494E-85E2-577CC5C4A5F0}">
   <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultColWidth="7.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="7.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" customWidth="1"/>
-    <col min="4" max="4" width="14.5546875" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
-    <col min="7" max="8" width="15.109375" customWidth="1"/>
-    <col min="9" max="9" width="15.44140625" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="7" max="8" width="15.140625" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="15.6">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -738,10 +768,10 @@
         <v>14</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06C4A4B-14A2-464D-BED4-E8DF83ADDABB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DAD94C8-FF28-4339-ABE4-11CCC09A6490}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="相关课程" sheetId="2" r:id="rId2"/>
     <sheet name="相关设备" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
   <si>
     <t>代理商</t>
   </si>
@@ -134,9 +134,6 @@
     <t>探头特殊剩余名额</t>
   </si>
   <si>
-    <t>探头高值剩余名额</t>
-  </si>
-  <si>
     <t>培训合同号</t>
   </si>
   <si>
@@ -144,12 +141,6 @@
   </si>
   <si>
     <t>探头特殊已使用名额</t>
-  </si>
-  <si>
-    <t>探头高值总额</t>
-  </si>
-  <si>
-    <t>探头高值已使用名额</t>
   </si>
   <si>
     <t>探头任意总额</t>
@@ -562,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -573,18 +564,17 @@
     <col min="9" max="9" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.42578125" customWidth="1"/>
     <col min="11" max="11" width="15.85546875" customWidth="1"/>
-    <col min="12" max="21" width="21.85546875" customWidth="1"/>
-    <col min="22" max="22" width="17.28515625" customWidth="1"/>
-    <col min="23" max="23" width="16.7109375" customWidth="1"/>
-    <col min="24" max="24" width="19.42578125" customWidth="1"/>
-    <col min="25" max="25" width="21.42578125" customWidth="1"/>
-    <col min="26" max="26" width="23.28515625" customWidth="1"/>
-    <col min="27" max="27" width="26.5703125" customWidth="1"/>
-    <col min="28" max="28" width="29.140625" customWidth="1"/>
-    <col min="29" max="29" width="16.42578125" customWidth="1"/>
+    <col min="12" max="19" width="21.85546875" customWidth="1"/>
+    <col min="20" max="20" width="16.7109375" customWidth="1"/>
+    <col min="21" max="21" width="19.42578125" customWidth="1"/>
+    <col min="22" max="22" width="21.42578125" customWidth="1"/>
+    <col min="23" max="23" width="23.28515625" customWidth="1"/>
+    <col min="24" max="24" width="26.5703125" customWidth="1"/>
+    <col min="25" max="25" width="29.140625" customWidth="1"/>
+    <col min="26" max="26" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
@@ -616,64 +606,55 @@
         <v>24</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>30</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="O1" s="5" t="s">
         <v>31</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="R1" s="5" t="s">
         <v>32</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="V1" s="5" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="X1" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y1" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z1" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB1" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC1" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="E12" s="6"/>
     </row>
   </sheetData>
@@ -702,7 +683,7 @@
         <v>6</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>7</v>
@@ -711,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>15</v>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DAD94C8-FF28-4339-ABE4-11CCC09A6490}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F339108-B754-4B86-889E-55A2B269E9AF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
     <sheet name="相关课程" sheetId="2" r:id="rId2"/>
     <sheet name="相关设备" sheetId="3" r:id="rId3"/>
+    <sheet name="相关高值探头" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
   <si>
     <t>代理商</t>
   </si>
@@ -156,6 +157,12 @@
   </si>
   <si>
     <t>探头特殊总额</t>
+  </si>
+  <si>
+    <t>SN编号</t>
+  </si>
+  <si>
+    <t>状态</t>
   </si>
 </sst>
 </file>
@@ -768,4 +775,36 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C997223-3E12-4485-8E5F-5DE43B6F30CA}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="24.85546875" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576" xr:uid="{DBCCAA88-FA78-48C9-8083-1825F8C7B982}">
+      <formula1>"可用,不可用"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F339108-B754-4B86-889E-55A2B269E9AF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11B30FC-034A-45D6-BB02-C2002274FAC7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="相关设备" sheetId="3" r:id="rId3"/>
     <sheet name="相关高值探头" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
   <si>
     <t>代理商</t>
   </si>
@@ -163,6 +163,9 @@
   </si>
   <si>
     <t>状态</t>
+  </si>
+  <si>
+    <t>名额扣除类型</t>
   </si>
 </sst>
 </file>
@@ -560,28 +563,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="14.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="7" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.42578125" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" customWidth="1"/>
-    <col min="12" max="19" width="21.85546875" customWidth="1"/>
-    <col min="20" max="20" width="16.7109375" customWidth="1"/>
-    <col min="21" max="21" width="19.42578125" customWidth="1"/>
-    <col min="22" max="22" width="21.42578125" customWidth="1"/>
-    <col min="23" max="23" width="23.28515625" customWidth="1"/>
-    <col min="24" max="24" width="26.5703125" customWidth="1"/>
-    <col min="25" max="25" width="29.140625" customWidth="1"/>
-    <col min="26" max="26" width="16.42578125" customWidth="1"/>
+    <col min="6" max="7" width="15.140625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" customWidth="1"/>
+    <col min="12" max="12" width="15.85546875" customWidth="1"/>
+    <col min="13" max="20" width="21.85546875" customWidth="1"/>
+    <col min="21" max="21" width="16.7109375" customWidth="1"/>
+    <col min="22" max="22" width="19.42578125" customWidth="1"/>
+    <col min="23" max="23" width="21.42578125" customWidth="1"/>
+    <col min="24" max="24" width="23.28515625" customWidth="1"/>
+    <col min="25" max="25" width="26.5703125" customWidth="1"/>
+    <col min="26" max="26" width="29.140625" customWidth="1"/>
+    <col min="27" max="27" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
@@ -601,70 +604,78 @@
         <v>3</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="U1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="X1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="Y1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Z1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="AA1" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="E12" s="6"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576" xr:uid="{B9BB85D7-67BD-4DFD-82F9-DAF2AE68BD61}">
+      <formula1>"新逻辑,旧逻辑"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11B30FC-034A-45D6-BB02-C2002274FAC7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06661D4-7E86-4D60-B1D2-59E5C8F1892B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -673,7 +673,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576" xr:uid="{B9BB85D7-67BD-4DFD-82F9-DAF2AE68BD61}">
-      <formula1>"新逻辑,旧逻辑"</formula1>
+      <formula1>"新逻辑扣除,旧逻辑扣除"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06661D4-7E86-4D60-B1D2-59E5C8F1892B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D348F2D4-B220-4988-BCE2-9CE874B7E889}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
   <si>
     <t>代理商</t>
   </si>
@@ -163,9 +163,6 @@
   </si>
   <si>
     <t>状态</t>
-  </si>
-  <si>
-    <t>名额扣除类型</t>
   </si>
 </sst>
 </file>
@@ -563,28 +560,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:AA12"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="14.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="15.140625" style="7" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.42578125" customWidth="1"/>
-    <col min="12" max="12" width="15.85546875" customWidth="1"/>
-    <col min="13" max="20" width="21.85546875" customWidth="1"/>
-    <col min="21" max="21" width="16.7109375" customWidth="1"/>
-    <col min="22" max="22" width="19.42578125" customWidth="1"/>
-    <col min="23" max="23" width="21.42578125" customWidth="1"/>
-    <col min="24" max="24" width="23.28515625" customWidth="1"/>
-    <col min="25" max="25" width="26.5703125" customWidth="1"/>
-    <col min="26" max="26" width="29.140625" customWidth="1"/>
-    <col min="27" max="27" width="16.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="7" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.42578125" customWidth="1"/>
+    <col min="11" max="11" width="15.85546875" customWidth="1"/>
+    <col min="12" max="19" width="21.85546875" customWidth="1"/>
+    <col min="20" max="20" width="16.7109375" customWidth="1"/>
+    <col min="21" max="21" width="19.42578125" customWidth="1"/>
+    <col min="22" max="22" width="21.42578125" customWidth="1"/>
+    <col min="23" max="23" width="23.28515625" customWidth="1"/>
+    <col min="24" max="24" width="26.5703125" customWidth="1"/>
+    <col min="25" max="25" width="29.140625" customWidth="1"/>
+    <col min="26" max="26" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
@@ -604,78 +601,70 @@
         <v>3</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V1" s="5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="X1" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y1" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Z1" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA1" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="E12" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576" xr:uid="{B9BB85D7-67BD-4DFD-82F9-DAF2AE68BD61}">
-      <formula1>"新逻辑扣除,旧逻辑扣除"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D348F2D4-B220-4988-BCE2-9CE874B7E889}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A2A5EDB-0BCD-426C-B80B-F859EF17A90C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
   <si>
     <t>代理商</t>
   </si>
@@ -163,6 +163,9 @@
   </si>
   <si>
     <t>状态</t>
+  </si>
+  <si>
+    <t>名额扣除类型</t>
   </si>
 </sst>
 </file>
@@ -560,28 +563,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="14.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="7" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.42578125" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" customWidth="1"/>
-    <col min="12" max="19" width="21.85546875" customWidth="1"/>
-    <col min="20" max="20" width="16.7109375" customWidth="1"/>
-    <col min="21" max="21" width="19.42578125" customWidth="1"/>
-    <col min="22" max="22" width="21.42578125" customWidth="1"/>
-    <col min="23" max="23" width="23.28515625" customWidth="1"/>
-    <col min="24" max="24" width="26.5703125" customWidth="1"/>
-    <col min="25" max="25" width="29.140625" customWidth="1"/>
-    <col min="26" max="26" width="16.42578125" customWidth="1"/>
+    <col min="6" max="7" width="15.140625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" customWidth="1"/>
+    <col min="12" max="12" width="15.85546875" customWidth="1"/>
+    <col min="13" max="20" width="21.85546875" customWidth="1"/>
+    <col min="21" max="21" width="16.7109375" customWidth="1"/>
+    <col min="22" max="22" width="19.42578125" customWidth="1"/>
+    <col min="23" max="23" width="21.42578125" customWidth="1"/>
+    <col min="24" max="24" width="23.28515625" customWidth="1"/>
+    <col min="25" max="25" width="26.5703125" customWidth="1"/>
+    <col min="26" max="26" width="29.140625" customWidth="1"/>
+    <col min="27" max="27" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
@@ -601,70 +604,78 @@
         <v>3</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="U1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="X1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="Y1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Z1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="AA1" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="E12" s="6"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576" xr:uid="{60CBBEE4-F24A-44F1-98D5-E38DCD3608A3}">
+      <formula1>"旧逻辑扣除,新逻辑扣除"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A2A5EDB-0BCD-426C-B80B-F859EF17A90C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53561785-8C2B-4A0F-ABA2-1BFB0050DDA4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -234,7 +234,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -249,6 +249,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -570,18 +573,19 @@
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="14.42578125" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="15.140625" style="7" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.42578125" customWidth="1"/>
-    <col min="12" max="12" width="15.85546875" customWidth="1"/>
-    <col min="13" max="20" width="21.85546875" customWidth="1"/>
-    <col min="21" max="21" width="16.7109375" customWidth="1"/>
-    <col min="22" max="22" width="19.42578125" customWidth="1"/>
-    <col min="23" max="23" width="21.42578125" customWidth="1"/>
-    <col min="24" max="24" width="23.28515625" customWidth="1"/>
-    <col min="25" max="25" width="26.5703125" customWidth="1"/>
-    <col min="26" max="26" width="29.140625" customWidth="1"/>
-    <col min="27" max="27" width="16.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="2"/>
+    <col min="9" max="9" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="15.85546875" style="2" customWidth="1"/>
+    <col min="13" max="20" width="21.85546875" style="2" customWidth="1"/>
+    <col min="21" max="21" width="16.7109375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="19.42578125" style="2" customWidth="1"/>
+    <col min="23" max="23" width="21.42578125" style="2" customWidth="1"/>
+    <col min="24" max="24" width="23.28515625" style="2" customWidth="1"/>
+    <col min="25" max="25" width="26.5703125" style="2" customWidth="1"/>
+    <col min="26" max="26" width="29.140625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="16.42578125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -606,64 +610,64 @@
       <c r="G1" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="W1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="X1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Y1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="Z1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AA1" s="8" t="s">
         <v>27</v>
       </c>
     </row>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53561785-8C2B-4A0F-ABA2-1BFB0050DDA4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A838531B-54FF-4C4B-9CA3-6ED30FE6708D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -675,9 +675,12 @@
       <c r="E12" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576" xr:uid="{60CBBEE4-F24A-44F1-98D5-E38DCD3608A3}">
       <formula1>"旧逻辑扣除,新逻辑扣除"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{3BD0C33C-69D3-4601-8939-6CE95574B014}">
+      <formula1>"PCB,Biomed,CCS,DI,PCB MVS"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A838531B-54FF-4C4B-9CA3-6ED30FE6708D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC6C60D-4339-4543-910E-8F21C6C8F11C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -677,7 +677,7 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576" xr:uid="{60CBBEE4-F24A-44F1-98D5-E38DCD3608A3}">
-      <formula1>"旧逻辑扣除,新逻辑扣除"</formula1>
+      <formula1>"旧逻辑扣减,新逻辑扣减"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{3BD0C33C-69D3-4601-8939-6CE95574B014}">
       <formula1>"PCB,Biomed,CCS,DI,PCB MVS"</formula1>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC6C60D-4339-4543-910E-8F21C6C8F11C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45366164-FB74-44C2-BE79-01C2BE1F514E}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
   <si>
     <t>代理商</t>
   </si>
@@ -166,6 +166,9 @@
   </si>
   <si>
     <t>名额扣除类型</t>
+  </si>
+  <si>
+    <t>是否ZKB 599方案</t>
   </si>
 </sst>
 </file>
@@ -566,29 +569,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:AA12"/>
+  <dimension ref="A1:AB12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="15.140625" style="7" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="2"/>
-    <col min="9" max="9" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.42578125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="15.85546875" style="2" customWidth="1"/>
-    <col min="13" max="20" width="21.85546875" style="2" customWidth="1"/>
-    <col min="21" max="21" width="16.7109375" style="2" customWidth="1"/>
-    <col min="22" max="22" width="19.42578125" style="2" customWidth="1"/>
-    <col min="23" max="23" width="21.42578125" style="2" customWidth="1"/>
-    <col min="24" max="24" width="23.28515625" style="2" customWidth="1"/>
-    <col min="25" max="25" width="26.5703125" style="2" customWidth="1"/>
-    <col min="26" max="26" width="29.140625" style="2" customWidth="1"/>
-    <col min="27" max="27" width="16.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="20.85546875" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="15.140625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.42578125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="15.85546875" style="2" customWidth="1"/>
+    <col min="14" max="21" width="21.85546875" style="2" customWidth="1"/>
+    <col min="22" max="22" width="16.7109375" style="2" customWidth="1"/>
+    <col min="23" max="23" width="19.42578125" style="2" customWidth="1"/>
+    <col min="24" max="24" width="21.42578125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="23.28515625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="26.5703125" style="2" customWidth="1"/>
+    <col min="27" max="27" width="29.140625" style="2" customWidth="1"/>
+    <col min="28" max="28" width="16.42578125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
@@ -599,88 +603,94 @@
         <v>6</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="R1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="S1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="T1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="U1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="V1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="8" t="s">
+      <c r="W1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="8" t="s">
+      <c r="X1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="X1" s="8" t="s">
+      <c r="Y1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="Y1" s="8" t="s">
+      <c r="Z1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="Z1" s="8" t="s">
+      <c r="AA1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="AA1" s="8" t="s">
+      <c r="AB1" s="8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="E12" s="6"/>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F12" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576" xr:uid="{60CBBEE4-F24A-44F1-98D5-E38DCD3608A3}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576" xr:uid="{60CBBEE4-F24A-44F1-98D5-E38DCD3608A3}">
       <formula1>"旧逻辑扣减,新逻辑扣减"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{3BD0C33C-69D3-4601-8939-6CE95574B014}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576" xr:uid="{3BD0C33C-69D3-4601-8939-6CE95574B014}">
       <formula1>"PCB,Biomed,CCS,DI,PCB MVS"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{8A3EC725-C6D7-44AB-939D-282FED68DD34}">
+      <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45366164-FB74-44C2-BE79-01C2BE1F514E}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9E8AB8-83ED-49FC-B31C-0F2DD5773A11}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -684,7 +684,7 @@
   </sheetData>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576" xr:uid="{60CBBEE4-F24A-44F1-98D5-E38DCD3608A3}">
-      <formula1>"旧逻辑扣减,新逻辑扣减"</formula1>
+      <formula1>"旧逻辑扣减,新逻辑扣减,N/A"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576" xr:uid="{3BD0C33C-69D3-4601-8939-6CE95574B014}">
       <formula1>"PCB,Biomed,CCS,DI,PCB MVS"</formula1>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9E8AB8-83ED-49FC-B31C-0F2DD5773A11}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8955E05-F6DA-4491-A71A-0BFEED08A213}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
   <si>
     <t>代理商</t>
   </si>
@@ -169,6 +169,9 @@
   </si>
   <si>
     <t>是否ZKB 599方案</t>
+  </si>
+  <si>
+    <t>是否代理商自身原因未完成培训</t>
   </si>
 </sst>
 </file>
@@ -748,7 +751,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEEB4E3A-F934-494E-85E2-577CC5C4A5F0}">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultColWidth="7.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -758,10 +761,11 @@
     <col min="5" max="5" width="12.42578125" customWidth="1"/>
     <col min="6" max="6" width="14.7109375" customWidth="1"/>
     <col min="7" max="8" width="15.140625" customWidth="1"/>
-    <col min="9" max="9" width="15.42578125" customWidth="1"/>
+    <col min="9" max="9" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -787,17 +791,23 @@
         <v>29</v>
       </c>
       <c r="I1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>28</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576" xr:uid="{B075DA68-B71A-4E5B-9F5B-32052F1603BD}">
       <formula1>"超声高端机,超声低端机,N/A"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576" xr:uid="{B1DF22E0-479B-4685-B17A-2952F9A994AD}">
       <formula1>"内修,外修,内外修可选"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1048576" xr:uid="{D6442C2E-EABA-4DF3-8895-F9463E167B67}">
+      <formula1>"N/A,是,否"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8955E05-F6DA-4491-A71A-0BFEED08A213}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF59914E-4CCD-4DDB-AFFC-3F02151EE9BC}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="11385" activeTab="3" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="47">
   <si>
     <t>代理商</t>
   </si>
@@ -172,13 +172,16 @@
   </si>
   <si>
     <t>是否代理商自身原因未完成培训</t>
+  </si>
+  <si>
+    <t>ps：如果需要导入四合一请输入编码【FourInOne】</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -204,16 +207,27 @@
       <color rgb="FF172B4D"/>
       <name val="宋体"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -236,11 +250,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -256,6 +281,9 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -817,15 +845,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C997223-3E12-4485-8E5F-5DE43B6F30CA}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
     <col min="2" max="2" width="24.85546875" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="53.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -834,6 +863,9 @@
       </c>
       <c r="C1" s="3" t="s">
         <v>42</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF59914E-4CCD-4DDB-AFFC-3F02151EE9BC}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D3DA579-9B86-45CA-B121-E907BD684A81}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="11385" activeTab="3" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
   <si>
     <t>代理商</t>
   </si>
@@ -175,6 +175,9 @@
   </si>
   <si>
     <t>ps：如果需要导入四合一请输入编码【FourInOne】</t>
+  </si>
+  <si>
+    <t>ps：‘Y’表示删除设备</t>
   </si>
 </sst>
 </file>
@@ -779,7 +782,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEEB4E3A-F934-494E-85E2-577CC5C4A5F0}">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr defaultColWidth="7.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -791,9 +794,10 @@
     <col min="7" max="8" width="15.140625" customWidth="1"/>
     <col min="9" max="9" width="33.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.42578125" customWidth="1"/>
+    <col min="11" max="11" width="58.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -823,6 +827,9 @@
       </c>
       <c r="J1" s="3" t="s">
         <v>28</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D3DA579-9B86-45CA-B121-E907BD684A81}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D016D37-48AA-4245-971E-573F85579ABB}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -836,7 +836,7 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576" xr:uid="{B075DA68-B71A-4E5B-9F5B-32052F1603BD}">
-      <formula1>"超声高端机,超声低端机,N/A"</formula1>
+      <formula1>"超声高端机,超声低端机,N/A,depot"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576" xr:uid="{B1DF22E0-479B-4685-B17A-2952F9A994AD}">
       <formula1>"内修,外修,内外修可选"</formula1>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D016D37-48AA-4245-971E-573F85579ABB}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C200BEFB-1829-45B6-BCBE-20265EB6BA59}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
   <si>
     <t>代理商</t>
   </si>
@@ -177,7 +177,10 @@
     <t>ps：如果需要导入四合一请输入编码【FourInOne】</t>
   </si>
   <si>
-    <t>ps：‘Y’表示删除设备</t>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>ps：‘Y’表示删除设备，删除设备时ID需要必填，ID可以从合同导出的excel中获取</t>
   </si>
 </sst>
 </file>
@@ -782,7 +785,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEEB4E3A-F934-494E-85E2-577CC5C4A5F0}">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultColWidth="7.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -793,11 +796,12 @@
     <col min="6" max="6" width="14.7109375" customWidth="1"/>
     <col min="7" max="8" width="15.140625" customWidth="1"/>
     <col min="9" max="9" width="33.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.42578125" customWidth="1"/>
-    <col min="11" max="11" width="58.140625" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" customWidth="1"/>
+    <col min="12" max="12" width="83.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -826,10 +830,13 @@
         <v>45</v>
       </c>
       <c r="J1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="9" t="s">
-        <v>47</v>
+      <c r="L1" s="9" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C200BEFB-1829-45B6-BCBE-20265EB6BA59}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C3BE25-95E2-497D-9455-19D1BB622E51}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C3BE25-95E2-497D-9455-19D1BB622E51}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6851DE-8FDA-4C9C-ABC6-38C05FB9EF1B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6851DE-8FDA-4C9C-ABC6-38C05FB9EF1B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC4DD6F-021C-4B6C-ABA5-50CB714F2783}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="50">
   <si>
     <t>代理商</t>
   </si>
@@ -181,6 +181,9 @@
   </si>
   <si>
     <t>ps：‘Y’表示删除设备，删除设备时ID需要必填，ID可以从合同导出的excel中获取</t>
+  </si>
+  <si>
+    <t>是否由GE FE提供年度1次现场保养</t>
   </si>
 </sst>
 </file>
@@ -785,7 +788,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEEB4E3A-F934-494E-85E2-577CC5C4A5F0}">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultColWidth="7.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -796,12 +799,13 @@
     <col min="6" max="6" width="14.7109375" customWidth="1"/>
     <col min="7" max="8" width="15.140625" customWidth="1"/>
     <col min="9" max="9" width="33.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" customWidth="1"/>
-    <col min="12" max="12" width="83.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="33.85546875" customWidth="1"/>
+    <col min="11" max="11" width="22" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" customWidth="1"/>
+    <col min="13" max="13" width="83.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -830,18 +834,21 @@
         <v>45</v>
       </c>
       <c r="J1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>48</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576" xr:uid="{B075DA68-B71A-4E5B-9F5B-32052F1603BD}">
       <formula1>"超声高端机,超声低端机,N/A,depot"</formula1>
     </dataValidation>
@@ -850,6 +857,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1048576" xr:uid="{D6442C2E-EABA-4DF3-8895-F9463E167B67}">
       <formula1>"N/A,是,否"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576" xr:uid="{9E03DDA7-0116-4857-8465-B66D9B4E9493}">
+      <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC4DD6F-021C-4B6C-ABA5-50CB714F2783}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E2092C-EBF0-4D4E-9394-FF9C2B3E5105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
   <si>
     <t>代理商</t>
   </si>
@@ -184,6 +184,9 @@
   </si>
   <si>
     <t>是否由GE FE提供年度1次现场保养</t>
+  </si>
+  <si>
+    <t>公司编码</t>
   </si>
 </sst>
 </file>
@@ -609,7 +612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -628,11 +631,11 @@
     <col min="24" max="24" width="21.42578125" style="2" customWidth="1"/>
     <col min="25" max="25" width="23.28515625" style="2" customWidth="1"/>
     <col min="26" max="26" width="26.5703125" style="2" customWidth="1"/>
-    <col min="27" max="27" width="29.140625" style="2" customWidth="1"/>
-    <col min="28" max="28" width="16.42578125" style="2" customWidth="1"/>
+    <col min="27" max="28" width="29.140625" style="2" customWidth="1"/>
+    <col min="29" max="29" width="16.42578125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
@@ -715,10 +718,13 @@
         <v>26</v>
       </c>
       <c r="AB1" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC1" s="8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="F12" s="6"/>
     </row>
   </sheetData>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E2092C-EBF0-4D4E-9394-FF9C2B3E5105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD321548-0C0D-49DF-B650-A7EC2C956384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="53">
   <si>
     <t>代理商</t>
   </si>
@@ -187,6 +187,12 @@
   </si>
   <si>
     <t>公司编码</t>
+  </si>
+  <si>
+    <t>599合同年份</t>
+  </si>
+  <si>
+    <t>关联合同号</t>
   </si>
 </sst>
 </file>
@@ -612,30 +618,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AE12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.85546875" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="15.140625" style="7" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" style="2"/>
-    <col min="10" max="10" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.42578125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="15.85546875" style="2" customWidth="1"/>
-    <col min="14" max="21" width="21.85546875" style="2" customWidth="1"/>
-    <col min="22" max="22" width="16.7109375" style="2" customWidth="1"/>
-    <col min="23" max="23" width="19.42578125" style="2" customWidth="1"/>
-    <col min="24" max="24" width="21.42578125" style="2" customWidth="1"/>
-    <col min="25" max="25" width="23.28515625" style="2" customWidth="1"/>
-    <col min="26" max="26" width="26.5703125" style="2" customWidth="1"/>
-    <col min="27" max="28" width="29.140625" style="2" customWidth="1"/>
-    <col min="29" max="29" width="16.42578125" style="2" customWidth="1"/>
+    <col min="4" max="6" width="20.85546875" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="15.140625" style="7" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="2"/>
+    <col min="12" max="12" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.42578125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="15.85546875" style="2" customWidth="1"/>
+    <col min="16" max="23" width="21.85546875" style="2" customWidth="1"/>
+    <col min="24" max="24" width="16.7109375" style="2" customWidth="1"/>
+    <col min="25" max="25" width="19.42578125" style="2" customWidth="1"/>
+    <col min="26" max="26" width="21.42578125" style="2" customWidth="1"/>
+    <col min="27" max="27" width="23.28515625" style="2" customWidth="1"/>
+    <col min="28" max="28" width="26.5703125" style="2" customWidth="1"/>
+    <col min="29" max="30" width="29.140625" style="2" customWidth="1"/>
+    <col min="31" max="31" width="16.42578125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
@@ -649,94 +655,103 @@
         <v>44</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="R1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="S1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="T1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="U1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="V1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="W1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="V1" s="8" t="s">
+      <c r="X1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="W1" s="8" t="s">
+      <c r="Y1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="8" t="s">
+      <c r="Z1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="Y1" s="8" t="s">
+      <c r="AA1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="Z1" s="8" t="s">
+      <c r="AB1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="AA1" s="8" t="s">
+      <c r="AC1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="8" t="s">
+      <c r="AD1" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="AC1" s="8" t="s">
+      <c r="AE1" s="8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="F12" s="6"/>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="H12" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576" xr:uid="{60CBBEE4-F24A-44F1-98D5-E38DCD3608A3}">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576" xr:uid="{60CBBEE4-F24A-44F1-98D5-E38DCD3608A3}">
       <formula1>"旧逻辑扣减,新逻辑扣减,N/A"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576" xr:uid="{3BD0C33C-69D3-4601-8939-6CE95574B014}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576" xr:uid="{3BD0C33C-69D3-4601-8939-6CE95574B014}">
       <formula1>"PCB,Biomed,CCS,DI,PCB MVS"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{8A3EC725-C6D7-44AB-939D-282FED68DD34}">
       <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576" xr:uid="{D9DD434F-1321-477E-91D3-065BB56A1B86}">
+      <formula1>"599合同第一年,599合同第2和3年"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD321548-0C0D-49DF-B650-A7EC2C956384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF9C330-3868-491B-A2E5-B8ECE1D16DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF9C330-3868-491B-A2E5-B8ECE1D16DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F20D12A-306E-42BB-A6C7-FBBDC70B6588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="54">
   <si>
     <t>代理商</t>
   </si>
@@ -193,6 +193,9 @@
   </si>
   <si>
     <t>关联合同号</t>
+  </si>
+  <si>
+    <t>2022年起探头高低端名额分类</t>
   </si>
 </sst>
 </file>
@@ -618,30 +621,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:AE12"/>
+  <dimension ref="A1:AF12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="20.85546875" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="14.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="15.140625" style="7" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" style="2"/>
-    <col min="12" max="12" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.42578125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="15.85546875" style="2" customWidth="1"/>
-    <col min="16" max="23" width="21.85546875" style="2" customWidth="1"/>
-    <col min="24" max="24" width="16.7109375" style="2" customWidth="1"/>
-    <col min="25" max="25" width="19.42578125" style="2" customWidth="1"/>
-    <col min="26" max="26" width="21.42578125" style="2" customWidth="1"/>
-    <col min="27" max="27" width="23.28515625" style="2" customWidth="1"/>
-    <col min="28" max="28" width="26.5703125" style="2" customWidth="1"/>
-    <col min="29" max="30" width="29.140625" style="2" customWidth="1"/>
-    <col min="31" max="31" width="16.42578125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" style="7" customWidth="1"/>
+    <col min="10" max="10" width="18.28515625" style="7" customWidth="1"/>
+    <col min="11" max="11" width="31.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" style="2"/>
+    <col min="13" max="13" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.42578125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="15.85546875" style="2" customWidth="1"/>
+    <col min="17" max="24" width="21.85546875" style="2" customWidth="1"/>
+    <col min="25" max="25" width="16.7109375" style="2" customWidth="1"/>
+    <col min="26" max="26" width="19.42578125" style="2" customWidth="1"/>
+    <col min="27" max="27" width="21.42578125" style="2" customWidth="1"/>
+    <col min="28" max="28" width="23.28515625" style="2" customWidth="1"/>
+    <col min="29" max="29" width="26.5703125" style="2" customWidth="1"/>
+    <col min="30" max="31" width="29.140625" style="2" customWidth="1"/>
+    <col min="32" max="32" width="16.42578125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
@@ -672,71 +677,74 @@
       <c r="J1" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="R1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="S1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="T1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="U1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="V1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="8" t="s">
+      <c r="W1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="W1" s="8" t="s">
+      <c r="X1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="X1" s="8" t="s">
+      <c r="Y1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="Y1" s="8" t="s">
+      <c r="Z1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="8" t="s">
+      <c r="AA1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="8" t="s">
+      <c r="AB1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="AB1" s="8" t="s">
+      <c r="AC1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="AC1" s="8" t="s">
+      <c r="AD1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="AD1" s="8" t="s">
+      <c r="AE1" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="AE1" s="8" t="s">
+      <c r="AF1" s="8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="H12" s="6"/>
     </row>
   </sheetData>
@@ -747,7 +755,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576" xr:uid="{3BD0C33C-69D3-4601-8939-6CE95574B014}">
       <formula1>"PCB,Biomed,CCS,DI,PCB MVS"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{8A3EC725-C6D7-44AB-939D-282FED68DD34}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576 K2:K1048576" xr:uid="{8A3EC725-C6D7-44AB-939D-282FED68DD34}">
       <formula1>"是,否"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576" xr:uid="{D9DD434F-1321-477E-91D3-065BB56A1B86}">

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F20D12A-306E-42BB-A6C7-FBBDC70B6588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F35738F-99E3-48B9-B28B-1091E4614665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="60">
   <si>
     <t>代理商</t>
   </si>
@@ -196,13 +196,31 @@
   </si>
   <si>
     <t>2022年起探头高低端名额分类</t>
+  </si>
+  <si>
+    <t>保养总额</t>
+  </si>
+  <si>
+    <t>保养剩余名额</t>
+  </si>
+  <si>
+    <t>保养已使用名额</t>
+  </si>
+  <si>
+    <t>备件高值总额</t>
+  </si>
+  <si>
+    <t>备件高值剩余名额</t>
+  </si>
+  <si>
+    <t>备件高值已使用名额</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -232,6 +250,13 @@
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF172B4D"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -286,7 +311,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -305,6 +330,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -621,7 +649,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:AF12"/>
+  <dimension ref="A1:AL12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -642,11 +670,13 @@
     <col min="27" max="27" width="21.42578125" style="2" customWidth="1"/>
     <col min="28" max="28" width="23.28515625" style="2" customWidth="1"/>
     <col min="29" max="29" width="26.5703125" style="2" customWidth="1"/>
-    <col min="30" max="31" width="29.140625" style="2" customWidth="1"/>
-    <col min="32" max="32" width="16.42578125" style="2" customWidth="1"/>
+    <col min="30" max="30" width="29.140625" style="2" customWidth="1"/>
+    <col min="31" max="36" width="29.140625" customWidth="1"/>
+    <col min="37" max="37" width="29.140625" style="2" customWidth="1"/>
+    <col min="38" max="38" width="16.42578125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
@@ -737,14 +767,32 @@
       <c r="AD1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="AE1" s="8" t="s">
+      <c r="AE1" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF1" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="AG1" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH1" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI1" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="AJ1" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="AK1" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="AF1" s="8" t="s">
+      <c r="AL1" s="8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="H12" s="6"/>
     </row>
   </sheetData>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F35738F-99E3-48B9-B28B-1091E4614665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BAA425D-0B41-4401-A37E-7FC921D9B3E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -650,33 +650,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
   <dimension ref="A1:AL12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="20.88671875" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" style="7" customWidth="1"/>
-    <col min="10" max="10" width="18.28515625" style="7" customWidth="1"/>
-    <col min="11" max="11" width="31.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" style="2"/>
-    <col min="13" max="13" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.42578125" style="2" customWidth="1"/>
-    <col min="16" max="16" width="15.85546875" style="2" customWidth="1"/>
-    <col min="17" max="24" width="21.85546875" style="2" customWidth="1"/>
-    <col min="25" max="25" width="16.7109375" style="2" customWidth="1"/>
-    <col min="26" max="26" width="19.42578125" style="2" customWidth="1"/>
-    <col min="27" max="27" width="21.42578125" style="2" customWidth="1"/>
-    <col min="28" max="28" width="23.28515625" style="2" customWidth="1"/>
-    <col min="29" max="29" width="26.5703125" style="2" customWidth="1"/>
-    <col min="30" max="30" width="29.140625" style="2" customWidth="1"/>
-    <col min="31" max="36" width="29.140625" customWidth="1"/>
-    <col min="37" max="37" width="29.140625" style="2" customWidth="1"/>
-    <col min="38" max="38" width="16.42578125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="14.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.109375" style="7" customWidth="1"/>
+    <col min="10" max="10" width="18.33203125" style="7" customWidth="1"/>
+    <col min="11" max="11" width="31.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.109375" style="2"/>
+    <col min="13" max="13" width="9.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.44140625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="15.88671875" style="2" customWidth="1"/>
+    <col min="17" max="24" width="21.88671875" style="2" customWidth="1"/>
+    <col min="25" max="25" width="16.6640625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="19.44140625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="21.44140625" style="2" customWidth="1"/>
+    <col min="28" max="28" width="23.33203125" style="2" customWidth="1"/>
+    <col min="29" max="29" width="26.5546875" style="2" customWidth="1"/>
+    <col min="30" max="30" width="29.109375" style="2" customWidth="1"/>
+    <col min="31" max="36" width="29.109375" customWidth="1"/>
+    <col min="37" max="37" width="29.109375" style="2" customWidth="1"/>
+    <col min="38" max="38" width="16.44140625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
@@ -792,7 +792,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.3">
       <c r="H12" s="6"/>
     </row>
   </sheetData>
@@ -801,7 +801,7 @@
       <formula1>"旧逻辑扣减,新逻辑扣减,N/A"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576" xr:uid="{3BD0C33C-69D3-4601-8939-6CE95574B014}">
-      <formula1>"PCB,Biomed,CCS,DI,PCB MVS"</formula1>
+      <formula1>"PCB,Biomed,CCS,DI,PCB MVS,CCSB"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576 K2:K1048576" xr:uid="{8A3EC725-C6D7-44AB-939D-282FED68DD34}">
       <formula1>"是,否"</formula1>
@@ -818,19 +818,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD4DBF4-FEF1-4385-BAD9-BD07A4FA541B}">
   <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" customWidth="1"/>
-    <col min="5" max="5" width="20.85546875" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" customWidth="1"/>
+    <col min="1" max="1" width="11.88671875" customWidth="1"/>
+    <col min="2" max="2" width="19.5546875" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" customWidth="1"/>
+    <col min="5" max="5" width="20.88671875" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -866,23 +866,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEEB4E3A-F934-494E-85E2-577CC5C4A5F0}">
   <dimension ref="A1:M1"/>
-  <sheetFormatPr defaultColWidth="7.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="7.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
-    <col min="7" max="8" width="15.140625" customWidth="1"/>
-    <col min="9" max="9" width="33.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="33.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="7" max="8" width="15.109375" customWidth="1"/>
+    <col min="9" max="9" width="33.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="33.88671875" customWidth="1"/>
     <col min="11" max="11" width="22" customWidth="1"/>
-    <col min="12" max="12" width="15.42578125" customWidth="1"/>
-    <col min="13" max="13" width="83.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.44140625" customWidth="1"/>
+    <col min="13" max="13" width="83.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -947,15 +947,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C997223-3E12-4485-8E5F-5DE43B6F30CA}">
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" customWidth="1"/>
-    <col min="2" max="2" width="24.85546875" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" customWidth="1"/>
-    <col min="4" max="4" width="53.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="24.88671875" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" customWidth="1"/>
+    <col min="4" max="4" width="53.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BAA425D-0B41-4401-A37E-7FC921D9B3E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43A85EE1-4264-450F-9399-2F39B70BF19F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="68">
   <si>
     <t>代理商</t>
   </si>
@@ -214,30 +214,57 @@
   </si>
   <si>
     <t>备件高值已使用名额</t>
+  </si>
+  <si>
+    <t>Biomed</t>
+  </si>
+  <si>
+    <t>合同金额</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>East</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>aaaaaa</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>599合同第一年</t>
+  </si>
+  <si>
+    <t>100W/年以下</t>
+  </si>
+  <si>
+    <t>旧逻辑扣减</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -245,11 +272,15 @@
       <sz val="12"/>
       <color rgb="FF172B4D"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -257,6 +288,13 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -337,7 +375,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -353,7 +391,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -649,34 +687,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:AL12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:AM12"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="20.88671875" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="14.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.109375" style="7" customWidth="1"/>
-    <col min="10" max="10" width="18.33203125" style="7" customWidth="1"/>
-    <col min="11" max="11" width="31.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.109375" style="2"/>
-    <col min="13" max="13" width="9.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.44140625" style="2" customWidth="1"/>
-    <col min="16" max="16" width="15.88671875" style="2" customWidth="1"/>
-    <col min="17" max="24" width="21.88671875" style="2" customWidth="1"/>
-    <col min="25" max="25" width="16.6640625" style="2" customWidth="1"/>
-    <col min="26" max="26" width="19.44140625" style="2" customWidth="1"/>
-    <col min="27" max="27" width="21.44140625" style="2" customWidth="1"/>
-    <col min="28" max="28" width="23.33203125" style="2" customWidth="1"/>
-    <col min="29" max="29" width="26.5546875" style="2" customWidth="1"/>
-    <col min="30" max="30" width="29.109375" style="2" customWidth="1"/>
-    <col min="31" max="36" width="29.109375" customWidth="1"/>
-    <col min="37" max="37" width="29.109375" style="2" customWidth="1"/>
-    <col min="38" max="38" width="16.44140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="10.09375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="20.90234375" customWidth="1"/>
+    <col min="7" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.09375" style="7" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" style="7" customWidth="1"/>
+    <col min="12" max="12" width="31.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.09375" style="2"/>
+    <col min="14" max="14" width="9.90234375" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.42578125" style="2" customWidth="1"/>
+    <col min="17" max="17" width="15.90234375" style="2" customWidth="1"/>
+    <col min="18" max="25" width="21.90234375" style="2" customWidth="1"/>
+    <col min="26" max="26" width="16.6640625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="19.42578125" style="2" customWidth="1"/>
+    <col min="28" max="28" width="21.42578125" style="2" customWidth="1"/>
+    <col min="29" max="29" width="23.33203125" style="2" customWidth="1"/>
+    <col min="30" max="30" width="26.5703125" style="2" customWidth="1"/>
+    <col min="31" max="31" width="29.09375" style="2" customWidth="1"/>
+    <col min="32" max="37" width="29.09375" customWidth="1"/>
+    <col min="38" max="38" width="29.09375" style="2" customWidth="1"/>
+    <col min="39" max="39" width="16.42578125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="4" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:39" s="4" customFormat="1" ht="28.5" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
@@ -699,115 +738,154 @@
         <v>1</v>
       </c>
       <c r="H1" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="R1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="S1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="T1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="U1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="V1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="V1" s="8" t="s">
+      <c r="W1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="W1" s="8" t="s">
+      <c r="X1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="X1" s="8" t="s">
+      <c r="Y1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="Y1" s="8" t="s">
+      <c r="Z1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="Z1" s="8" t="s">
+      <c r="AA1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="AA1" s="8" t="s">
+      <c r="AB1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="8" t="s">
+      <c r="AC1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="AC1" s="8" t="s">
+      <c r="AD1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="AD1" s="8" t="s">
+      <c r="AE1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="AE1" s="10" t="s">
+      <c r="AF1" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="AF1" s="10" t="s">
+      <c r="AG1" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="AG1" s="10" t="s">
+      <c r="AH1" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="AH1" s="10" t="s">
+      <c r="AI1" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AI1" s="10" t="s">
+      <c r="AJ1" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="AJ1" s="10" t="s">
+      <c r="AK1" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="AK1" s="8" t="s">
+      <c r="AL1" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="AL1" s="8" t="s">
+      <c r="AM1" s="8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="H12" s="6"/>
+    <row r="2" spans="1:39">
+      <c r="A2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I2" s="7">
+        <v>44972</v>
+      </c>
+      <c r="J2" s="7">
+        <v>45337</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:39">
+      <c r="I12" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576" xr:uid="{60CBBEE4-F24A-44F1-98D5-E38DCD3608A3}">
+  <phoneticPr fontId="6" type="noConversion"/>
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K1048576" xr:uid="{60CBBEE4-F24A-44F1-98D5-E38DCD3608A3}">
       <formula1>"旧逻辑扣减,新逻辑扣减,N/A"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576" xr:uid="{3BD0C33C-69D3-4601-8939-6CE95574B014}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576 H3:H1048576" xr:uid="{3BD0C33C-69D3-4601-8939-6CE95574B014}">
       <formula1>"PCB,Biomed,CCS,DI,PCB MVS,CCSB"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576 K2:K1048576" xr:uid="{8A3EC725-C6D7-44AB-939D-282FED68DD34}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576 L2:L1048576" xr:uid="{8A3EC725-C6D7-44AB-939D-282FED68DD34}">
       <formula1>"是,否"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576" xr:uid="{D9DD434F-1321-477E-91D3-065BB56A1B86}">
       <formula1>"599合同第一年,599合同第2和3年"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2" xr:uid="{CCE731C6-AFBD-475B-A0DC-66F6569DBBDE}">
+      <formula1>"100W/年以下,100W/年以上"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -818,19 +896,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD4DBF4-FEF1-4385-BAD9-BD07A4FA541B}">
   <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="11.88671875" customWidth="1"/>
-    <col min="2" max="2" width="19.5546875" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="1" max="1" width="11.90234375" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
     <col min="4" max="4" width="17.6640625" customWidth="1"/>
-    <col min="5" max="5" width="20.88671875" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" customWidth="1"/>
+    <col min="5" max="5" width="20.90234375" customWidth="1"/>
+    <col min="6" max="6" width="15.90234375" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="15.3">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -866,23 +944,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEEB4E3A-F934-494E-85E2-577CC5C4A5F0}">
   <dimension ref="A1:M1"/>
-  <sheetFormatPr defaultColWidth="7.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="7.6640625" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="2" customWidth="1"/>
     <col min="3" max="3" width="13.33203125" customWidth="1"/>
-    <col min="4" max="4" width="14.5546875" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" customWidth="1"/>
     <col min="6" max="6" width="14.6640625" customWidth="1"/>
-    <col min="7" max="8" width="15.109375" customWidth="1"/>
-    <col min="9" max="9" width="33.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="33.88671875" customWidth="1"/>
+    <col min="7" max="8" width="15.09375" customWidth="1"/>
+    <col min="9" max="9" width="33.90234375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="33.90234375" customWidth="1"/>
     <col min="11" max="11" width="22" customWidth="1"/>
-    <col min="12" max="12" width="15.44140625" customWidth="1"/>
-    <col min="13" max="13" width="83.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" customWidth="1"/>
+    <col min="13" max="13" width="83.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" s="1" customFormat="1" ht="15.3">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -947,15 +1025,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C997223-3E12-4485-8E5F-5DE43B6F30CA}">
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="16.6640625" customWidth="1"/>
-    <col min="2" max="2" width="24.88671875" customWidth="1"/>
+    <col min="2" max="2" width="24.90234375" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" customWidth="1"/>
-    <col min="4" max="4" width="53.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="53.90234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15.3">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -970,6 +1048,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576" xr:uid="{DBCCAA88-FA78-48C9-8083-1825F8C7B982}">
       <formula1>"可用,不可用"</formula1>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43A85EE1-4264-450F-9399-2F39B70BF19F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD88907B-7586-4991-9C0A-1316FEE28BD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="61">
   <si>
     <t>代理商</t>
   </si>
@@ -214,33 +214,10 @@
   </si>
   <si>
     <t>备件高值已使用名额</t>
-  </si>
-  <si>
-    <t>Biomed</t>
   </si>
   <si>
     <t>合同金额</t>
     <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>East</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>aaaaaa</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>是</t>
-  </si>
-  <si>
-    <t>599合同第一年</t>
-  </si>
-  <si>
-    <t>100W/年以下</t>
-  </si>
-  <si>
-    <t>旧逻辑扣减</t>
   </si>
 </sst>
 </file>
@@ -738,7 +715,7 @@
         <v>1</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>2</v>
@@ -832,38 +809,6 @@
       </c>
       <c r="AM1" s="8" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:39">
-      <c r="A2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H2" t="s">
-        <v>66</v>
-      </c>
-      <c r="I2" s="7">
-        <v>44972</v>
-      </c>
-      <c r="J2" s="7">
-        <v>45337</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:39">
@@ -875,7 +820,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K1048576" xr:uid="{60CBBEE4-F24A-44F1-98D5-E38DCD3608A3}">
       <formula1>"旧逻辑扣减,新逻辑扣减,N/A"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576 H3:H1048576" xr:uid="{3BD0C33C-69D3-4601-8939-6CE95574B014}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576 H152:H1048576" xr:uid="{3BD0C33C-69D3-4601-8939-6CE95574B014}">
       <formula1>"PCB,Biomed,CCS,DI,PCB MVS,CCSB"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576 L2:L1048576" xr:uid="{8A3EC725-C6D7-44AB-939D-282FED68DD34}">
@@ -884,7 +829,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576" xr:uid="{D9DD434F-1321-477E-91D3-065BB56A1B86}">
       <formula1>"599合同第一年,599合同第2和3年"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2" xr:uid="{CCE731C6-AFBD-475B-A0DC-66F6569DBBDE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H151" xr:uid="{9A9A72BC-BC26-4AD9-9A2E-BF66E36F9B84}">
       <formula1>"100W/年以下,100W/年以上"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gehealthcare-my.sharepoint.com/personal/503189362_gehealthcare_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD88907B-7586-4991-9C0A-1316FEE28BD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{FD0D540E-DBFE-416C-9277-1A541D0DFF52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2D591D5-D3C1-419D-A4BE-AEC797182677}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="相关设备" sheetId="3" r:id="rId3"/>
     <sheet name="相关高值探头" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">相关设备!$K$1:$K$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
   <si>
     <t>代理商</t>
   </si>
@@ -218,6 +221,9 @@
   <si>
     <t>合同金额</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>zone</t>
   </si>
 </sst>
 </file>
@@ -228,20 +234,20 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -268,7 +274,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -352,7 +358,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -368,7 +374,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -666,30 +672,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AM12"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.09375" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="20.90234375" customWidth="1"/>
+    <col min="1" max="1" width="10.1015625" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="20.89453125" customWidth="1"/>
     <col min="7" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.09375" style="7" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" style="7" customWidth="1"/>
-    <col min="12" max="12" width="31.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.09375" style="2"/>
-    <col min="14" max="14" width="9.90234375" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.42578125" style="2" customWidth="1"/>
-    <col min="17" max="17" width="15.90234375" style="2" customWidth="1"/>
-    <col min="18" max="25" width="21.90234375" style="2" customWidth="1"/>
-    <col min="26" max="26" width="16.6640625" style="2" customWidth="1"/>
-    <col min="27" max="27" width="19.42578125" style="2" customWidth="1"/>
-    <col min="28" max="28" width="21.42578125" style="2" customWidth="1"/>
-    <col min="29" max="29" width="23.33203125" style="2" customWidth="1"/>
-    <col min="30" max="30" width="26.5703125" style="2" customWidth="1"/>
-    <col min="31" max="31" width="29.09375" style="2" customWidth="1"/>
-    <col min="32" max="37" width="29.09375" customWidth="1"/>
-    <col min="38" max="38" width="29.09375" style="2" customWidth="1"/>
-    <col min="39" max="39" width="16.42578125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="14.41796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.1015625" style="7" customWidth="1"/>
+    <col min="11" max="11" width="18.3125" style="7" customWidth="1"/>
+    <col min="12" max="12" width="31.41796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.1015625" style="2"/>
+    <col min="14" max="14" width="9.89453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.41796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.41796875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="15.89453125" style="2" customWidth="1"/>
+    <col min="18" max="25" width="21.89453125" style="2" customWidth="1"/>
+    <col min="26" max="26" width="16.68359375" style="2" customWidth="1"/>
+    <col min="27" max="27" width="19.41796875" style="2" customWidth="1"/>
+    <col min="28" max="28" width="21.41796875" style="2" customWidth="1"/>
+    <col min="29" max="29" width="23.3125" style="2" customWidth="1"/>
+    <col min="30" max="30" width="26.578125" style="2" customWidth="1"/>
+    <col min="31" max="31" width="29.1015625" style="2" customWidth="1"/>
+    <col min="32" max="37" width="29.1015625" customWidth="1"/>
+    <col min="38" max="38" width="29.1015625" style="2" customWidth="1"/>
+    <col min="39" max="39" width="16.41796875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" s="4" customFormat="1" ht="28.5" customHeight="1">
@@ -841,16 +847,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD4DBF4-FEF1-4385-BAD9-BD07A4FA541B}">
   <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.90234375" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" customWidth="1"/>
-    <col min="5" max="5" width="20.90234375" customWidth="1"/>
-    <col min="6" max="6" width="15.90234375" customWidth="1"/>
+    <col min="1" max="1" width="11.89453125" customWidth="1"/>
+    <col min="2" max="2" width="19.578125" customWidth="1"/>
+    <col min="3" max="3" width="16.41796875" customWidth="1"/>
+    <col min="4" max="4" width="17.68359375" customWidth="1"/>
+    <col min="5" max="5" width="20.89453125" customWidth="1"/>
+    <col min="6" max="6" width="15.89453125" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.68359375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.3">
@@ -888,24 +894,25 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEEB4E3A-F934-494E-85E2-577CC5C4A5F0}">
-  <dimension ref="A1:M1"/>
-  <sheetFormatPr defaultColWidth="7.6640625" defaultRowHeight="13.8"/>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr defaultColWidth="7.68359375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
-    <col min="7" max="8" width="15.09375" customWidth="1"/>
-    <col min="9" max="9" width="33.90234375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="33.90234375" customWidth="1"/>
-    <col min="11" max="11" width="22" customWidth="1"/>
-    <col min="12" max="12" width="15.42578125" customWidth="1"/>
-    <col min="13" max="13" width="83.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.41796875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.3125" customWidth="1"/>
+    <col min="4" max="4" width="14.578125" customWidth="1"/>
+    <col min="5" max="5" width="12.41796875" customWidth="1"/>
+    <col min="6" max="6" width="14.68359375" customWidth="1"/>
+    <col min="7" max="8" width="15.1015625" customWidth="1"/>
+    <col min="9" max="9" width="33.89453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="33.89453125" customWidth="1"/>
+    <col min="11" max="11" width="21.3671875" customWidth="1"/>
+    <col min="12" max="12" width="22" customWidth="1"/>
+    <col min="13" max="13" width="15.41796875" customWidth="1"/>
+    <col min="14" max="14" width="83.578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" ht="15.3">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="15.3">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -937,12 +944,15 @@
         <v>49</v>
       </c>
       <c r="K1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="N1" s="9" t="s">
         <v>48</v>
       </c>
     </row>
@@ -970,12 +980,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C997223-3E12-4485-8E5F-5DE43B6F30CA}">
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" customWidth="1"/>
-    <col min="2" max="2" width="24.90234375" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" customWidth="1"/>
-    <col min="4" max="4" width="53.90234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.68359375" customWidth="1"/>
+    <col min="2" max="2" width="24.89453125" customWidth="1"/>
+    <col min="3" max="3" width="20.68359375" customWidth="1"/>
+    <col min="4" max="4" width="53.89453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.3">

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gehealthcare-my.sharepoint.com/personal/503189362_gehealthcare_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Java Codes\company\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{FD0D540E-DBFE-416C-9277-1A541D0DFF52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2D591D5-D3C1-419D-A4BE-AEC797182677}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7CF52FF-796C-44D7-8D27-D4B473577482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Java Codes\company\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7CF52FF-796C-44D7-8D27-D4B473577482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D577D4-1AE0-4D8E-84F6-4CD1D0CF78B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="64">
   <si>
     <t>代理商</t>
   </si>
@@ -224,6 +224,12 @@
   </si>
   <si>
     <t>zone</t>
+  </si>
+  <si>
+    <t>积分是否清零</t>
+  </si>
+  <si>
+    <t>ps：‘Y’表示清零</t>
   </si>
 </sst>
 </file>
@@ -374,9 +380,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -414,7 +420,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -520,7 +526,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -662,7 +668,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -671,7 +677,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AM12"/>
+  <dimension ref="A1:AO12"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.1015625" bestFit="1" customWidth="1"/>
@@ -696,9 +702,11 @@
     <col min="32" max="37" width="29.1015625" customWidth="1"/>
     <col min="38" max="38" width="29.1015625" style="2" customWidth="1"/>
     <col min="39" max="39" width="16.41796875" style="2" customWidth="1"/>
+    <col min="40" max="40" width="16.7890625" customWidth="1"/>
+    <col min="41" max="41" width="24.41796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" s="4" customFormat="1" ht="28.5" customHeight="1">
+    <row r="1" spans="1:41" s="4" customFormat="1" ht="28.5" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
@@ -816,8 +824,14 @@
       <c r="AM1" s="8" t="s">
         <v>27</v>
       </c>
+      <c r="AN1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="AO1" s="9" t="s">
+        <v>63</v>
+      </c>
     </row>
-    <row r="12" spans="1:39">
+    <row r="12" spans="1:41">
       <c r="I12" s="6"/>
     </row>
   </sheetData>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Java Codes\company\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D577D4-1AE0-4D8E-84F6-4CD1D0CF78B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68305028-479B-444D-BB98-91A68A71CD11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="68">
   <si>
     <t>代理商</t>
   </si>
@@ -230,6 +230,18 @@
   </si>
   <si>
     <t>ps：‘Y’表示清零</t>
+  </si>
+  <si>
+    <t>耗材总额</t>
+  </si>
+  <si>
+    <t>耗材剩余名额</t>
+  </si>
+  <si>
+    <t>耗材已使用名额</t>
+  </si>
+  <si>
+    <t>耗材增幅</t>
   </si>
 </sst>
 </file>
@@ -677,7 +689,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AO12"/>
+  <dimension ref="A1:AS12"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.1015625" bestFit="1" customWidth="1"/>
@@ -700,13 +712,15 @@
     <col min="30" max="30" width="26.578125" style="2" customWidth="1"/>
     <col min="31" max="31" width="29.1015625" style="2" customWidth="1"/>
     <col min="32" max="37" width="29.1015625" customWidth="1"/>
-    <col min="38" max="38" width="29.1015625" style="2" customWidth="1"/>
+    <col min="38" max="38" width="11.41796875" style="2" customWidth="1"/>
     <col min="39" max="39" width="16.41796875" style="2" customWidth="1"/>
-    <col min="40" max="40" width="16.7890625" customWidth="1"/>
-    <col min="41" max="41" width="24.41796875" customWidth="1"/>
+    <col min="40" max="41" width="15.26171875" customWidth="1"/>
+    <col min="42" max="42" width="13.578125" customWidth="1"/>
+    <col min="43" max="43" width="10.3125" customWidth="1"/>
+    <col min="44" max="44" width="15.3125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" s="4" customFormat="1" ht="28.5" customHeight="1">
+    <row r="1" spans="1:45" s="4" customFormat="1" ht="28.5" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
@@ -818,20 +832,32 @@
       <c r="AK1" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="AL1" s="8" t="s">
+      <c r="AL1" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AM1" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN1" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AO1" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="AP1" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="AM1" s="8" t="s">
+      <c r="AQ1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="AN1" s="8" t="s">
+      <c r="AR1" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="AO1" s="9" t="s">
+      <c r="AS1" s="9" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:41">
+    <row r="12" spans="1:45">
       <c r="I12" s="6"/>
     </row>
   </sheetData>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Java Codes\company\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JavaCodes\company\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68305028-479B-444D-BB98-91A68A71CD11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCBF8E86-68DB-4FE6-86D0-B15FFF562303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="69">
   <si>
     <t>代理商</t>
   </si>
@@ -242,6 +242,9 @@
   </si>
   <si>
     <t>耗材增幅</t>
+  </si>
+  <si>
+    <t>是否可以申请工具箱</t>
   </si>
 </sst>
 </file>
@@ -689,7 +692,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AS12"/>
+  <dimension ref="A1:AT12"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.1015625" bestFit="1" customWidth="1"/>
@@ -716,11 +719,12 @@
     <col min="39" max="39" width="16.41796875" style="2" customWidth="1"/>
     <col min="40" max="41" width="15.26171875" customWidth="1"/>
     <col min="42" max="42" width="13.578125" customWidth="1"/>
-    <col min="43" max="43" width="10.3125" customWidth="1"/>
-    <col min="44" max="44" width="15.3125" customWidth="1"/>
+    <col min="43" max="43" width="20.7890625" customWidth="1"/>
+    <col min="44" max="44" width="10.3125" customWidth="1"/>
+    <col min="45" max="45" width="15.3125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" s="4" customFormat="1" ht="28.5" customHeight="1">
+    <row r="1" spans="1:46" s="4" customFormat="1" ht="28.5" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
@@ -848,16 +852,19 @@
         <v>50</v>
       </c>
       <c r="AQ1" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="AR1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="AR1" s="8" t="s">
+      <c r="AS1" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="AS1" s="9" t="s">
+      <c r="AT1" s="9" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:45">
+    <row r="12" spans="1:46">
       <c r="I12" s="6"/>
     </row>
   </sheetData>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_imp_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JavaCodes\company\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCBF8E86-68DB-4FE6-86D0-B15FFF562303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF8AC7E6-7302-496C-92CB-DE6A4117C2A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -869,14 +869,14 @@
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K1048576" xr:uid="{60CBBEE4-F24A-44F1-98D5-E38DCD3608A3}">
       <formula1>"旧逻辑扣减,新逻辑扣减,N/A"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576 H152:H1048576" xr:uid="{3BD0C33C-69D3-4601-8939-6CE95574B014}">
       <formula1>"PCB,Biomed,CCS,DI,PCB MVS,CCSB"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576 L2:L1048576" xr:uid="{8A3EC725-C6D7-44AB-939D-282FED68DD34}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576 L2:L1048576 AQ2" xr:uid="{8A3EC725-C6D7-44AB-939D-282FED68DD34}">
       <formula1>"是,否"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576" xr:uid="{D9DD434F-1321-477E-91D3-065BB56A1B86}">
@@ -884,6 +884,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H151" xr:uid="{9A9A72BC-BC26-4AD9-9A2E-BF66E36F9B84}">
       <formula1>"100W/年以下,100W/年以上"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ3:AQ1048576" xr:uid="{FC194FB9-F889-4C31-BC10-FC73247FA48E}">
+      <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
